--- a/stock.xlsx
+++ b/stock.xlsx
@@ -2437,7 +2437,7 @@
     <t>VVS</t>
   </si>
   <si>
-    <t>Công ty Cổ phần Khoáng sản Công nghiệp Yên Bái</t>
+    <t>Công ty Cổ phần YBM</t>
   </si>
   <si>
     <t>YBM</t>
